--- a/PublicTools/econfigs/4_charactersmagic.xlsx
+++ b/PublicTools/econfigs/4_charactersmagic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrew/ws.localized/arpgfun/PublicTools/econfigs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62B91F1-462F-D644-942B-5AC783C26B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F54E3B-EAAB-244E-9D6A-BF060A70DBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="__Base" sheetId="1" r:id="rId1"/>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="141">
   <si>
     <t>CharacterMagicData</t>
   </si>
@@ -385,16 +385,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>类型</t>
-  </si>
-  <si>
     <t>Int</t>
   </si>
   <si>
     <t>String</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
   <si>
     <t>名称</t>
@@ -506,9 +500,6 @@
   </si>
   <si>
     <t>释放出随身携带的小型泉眼</t>
-  </si>
-  <si>
-    <t>自然之雨</t>
   </si>
   <si>
     <t xml:space="preserve">自然之雨 </t>
@@ -703,12 +694,104 @@
     <t>skills/16_blizzard</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>魔法护盾</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>编号</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓箭射击</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炸弓箭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐身</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻影</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>光弹术</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>心灵救赎</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命之源</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然之雨</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球术</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电之源</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>混乱之雨</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑术</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>勇士之盾</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>勇士之怒</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>怒气之刃</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>皇家剑术</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>领袖之刃</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>皇权之怒</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -774,6 +857,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -826,7 +916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -843,6 +933,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -29028,18 +29119,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z998"/>
+  <dimension ref="A1:Z997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="52.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="21.1640625" customWidth="1"/>
+    <col min="4" max="4" width="53.1640625" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.1640625" customWidth="1"/>
     <col min="7" max="7" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5" customWidth="1"/>
-    <col min="9" max="9" width="9.5" customWidth="1"/>
+    <col min="8" max="8" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.33203125" customWidth="1"/>
     <col min="12" max="12" width="9.5" customWidth="1"/>
     <col min="13" max="13" width="10.1640625" customWidth="1"/>
@@ -29049,7 +29140,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>4</v>
@@ -29105,46 +29196,46 @@
     </row>
     <row r="2" spans="1:26" ht="16">
       <c r="A2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -29161,46 +29252,46 @@
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="M3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L3" s="12" t="s">
+      <c r="N3" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -29217,25 +29308,25 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -29273,25 +29364,25 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H5" s="3">
         <v>10</v>
@@ -29329,25 +29420,25 @@
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="B6" s="2">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H6" s="3">
         <v>20</v>
@@ -29385,25 +29476,25 @@
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="B7" s="2">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H7" s="3">
         <v>80</v>
@@ -29441,25 +29532,25 @@
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="B8" s="2">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" s="2">
         <v>2</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H8" s="3">
         <v>10</v>
@@ -29497,25 +29588,25 @@
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2">
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H9" s="2">
         <v>30</v>
@@ -29553,25 +29644,25 @@
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10" s="3">
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H10" s="3">
         <v>50</v>
@@ -29609,25 +29700,25 @@
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3">
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H11" s="3">
         <v>80</v>
@@ -29665,25 +29756,25 @@
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3">
         <v>3</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H12" s="3">
         <v>20</v>
@@ -29720,26 +29811,26 @@
       <c r="Z12" s="4"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>67</v>
+      <c r="A13" s="16" t="s">
+        <v>118</v>
       </c>
       <c r="B13" s="3">
         <v>13</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E13" s="3">
         <v>3</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H13" s="3">
         <v>60</v>
@@ -29751,7 +29842,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="L13" s="3">
         <v>3</v>
@@ -29777,25 +29868,25 @@
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="B14" s="3">
         <v>14</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E14" s="3">
         <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H14" s="3">
         <v>40</v>
@@ -29833,25 +29924,25 @@
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="B15" s="3">
         <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E15" s="3">
         <v>3</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -29889,25 +29980,25 @@
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="B16" s="3">
         <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E16" s="3">
         <v>4</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H16" s="3">
         <v>0</v>
@@ -29945,25 +30036,25 @@
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="B17" s="3">
         <v>18</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E17" s="3">
         <v>4</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H17" s="3">
         <v>10</v>
@@ -30001,25 +30092,25 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="B18" s="3">
         <v>19</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E18" s="3">
         <v>4</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H18" s="3">
         <v>40</v>
@@ -30057,25 +30148,25 @@
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3">
         <v>20</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E19" s="3">
         <v>4</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H19" s="3">
         <v>30</v>
@@ -30113,25 +30204,25 @@
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="B20" s="3">
         <v>21</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E20" s="3">
         <v>5</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -30169,25 +30260,25 @@
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="B21" s="3">
         <v>22</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H21" s="3">
         <v>15</v>
@@ -30225,25 +30316,25 @@
     </row>
     <row r="22" spans="1:26" ht="16">
       <c r="A22" s="9" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="B22" s="3">
         <v>23</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E22" s="3">
         <v>5</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>20</v>
@@ -30281,25 +30372,25 @@
     </row>
     <row r="23" spans="1:26" ht="16">
       <c r="A23" s="9" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="B23" s="3">
         <v>24</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E23" s="3">
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H23" s="3">
         <v>30</v>
@@ -30335,59 +30426,46 @@
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
     </row>
-    <row r="24" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>117</v>
+    <row r="24" spans="1:26" s="9" customFormat="1" ht="14" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>114</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="9">
         <v>1001</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>117</v>
+      <c r="C24" s="9" t="s">
+        <v>114</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>118</v>
+      <c r="D24" s="9" t="s">
+        <v>115</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="9">
         <v>-1</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4" t="s">
-        <v>119</v>
+      <c r="G24" s="9" t="s">
+        <v>116</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="9">
         <v>0</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="9">
         <v>0</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="9">
         <v>0</v>
       </c>
-      <c r="K24" s="4">
+      <c r="K24" s="9">
         <v>200</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L24" s="9">
         <v>1</v>
       </c>
-      <c r="M24" s="4">
+      <c r="M24" s="9">
         <v>4</v>
       </c>
-      <c r="N24" s="4">
+      <c r="N24" s="9">
         <v>1</v>
       </c>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="4"/>
-      <c r="X24" s="4"/>
-      <c r="Y24" s="4"/>
-      <c r="Z24" s="4"/>
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1">
       <c r="A25" s="4"/>
@@ -57633,34 +57711,6 @@
       <c r="Y997" s="4"/>
       <c r="Z997" s="4"/>
     </row>
-    <row r="998" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A998" s="4"/>
-      <c r="B998" s="4"/>
-      <c r="C998" s="4"/>
-      <c r="D998" s="4"/>
-      <c r="E998" s="4"/>
-      <c r="F998" s="4"/>
-      <c r="G998" s="4"/>
-      <c r="H998" s="4"/>
-      <c r="I998" s="4"/>
-      <c r="J998" s="4"/>
-      <c r="K998" s="4"/>
-      <c r="L998" s="4"/>
-      <c r="M998" s="4"/>
-      <c r="N998" s="4"/>
-      <c r="O998" s="4"/>
-      <c r="P998" s="4"/>
-      <c r="Q998" s="4"/>
-      <c r="R998" s="4"/>
-      <c r="S998" s="4"/>
-      <c r="T998" s="4"/>
-      <c r="U998" s="4"/>
-      <c r="V998" s="4"/>
-      <c r="W998" s="4"/>
-      <c r="X998" s="4"/>
-      <c r="Y998" s="4"/>
-      <c r="Z998" s="4"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="1">
@@ -57687,7 +57737,7 @@
     <row r="1" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="2" spans="1:2" ht="1.5" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
@@ -57695,7 +57745,7 @@
     </row>
     <row r="3" spans="1:2" ht="13.5" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B3" s="10">
         <v>1</v>
@@ -57703,7 +57753,7 @@
     </row>
     <row r="4" spans="1:2" ht="13.5" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B4" s="10">
         <v>2</v>
@@ -57711,7 +57761,7 @@
     </row>
     <row r="5" spans="1:2" ht="13.5" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B5" s="10">
         <v>2</v>
@@ -57719,7 +57769,7 @@
     </row>
     <row r="6" spans="1:2" ht="13.5" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B6" s="10">
         <v>1</v>
